--- a/cluster_infra_report.xlsx
+++ b/cluster_infra_report.xlsx
@@ -10,9 +10,7 @@
     <sheet name="Cluster_Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cluster_Node" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cluster_Pod" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cluster_Top_Nodes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cluster_Top_Pods" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cluster_HPA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cluster_Top_Pods" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -562,71 +560,66 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Highest node CPU usage</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>92</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>i-0b657e550bec4e711 at 92%</t>
-        </is>
-      </c>
+          <t>Node Group</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Highest node memory usage</t>
+          <t>Highest node CPU usage</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:05:00Z</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>i-0a100856b64c3798a at 101%</t>
+          <t>i-0b657e550bec4e711 at 92%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Average node CPU usage</t>
+          <t>Highest node memory usage</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.07</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical EC2 / CloudWatch</t>
+          <t>i-0a100856b64c3798a at 100%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Average node memory usage</t>
+          <t>Average node CPU usage</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73.67</v>
+        <v>5.13</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -642,18 +635,38 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Average node memory usage</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Historical EC2 / CloudWatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Nodes above 80% CPU</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Historical EC2 / CloudWatch</t>
         </is>
@@ -673,22 +686,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,60 +723,115 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Node Group</t>
+          <t>CPU Used Avg (cores)</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>CPU Used Avg (cores)</t>
+          <t>CPU Peak (cores)</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CPU Peak (cores)</t>
+          <t>Peak Observed Time</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Peak Observed Time</t>
+          <t>CPU Request (cores)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>CPU Request (cores)</t>
+          <t>Memory Used Avg (GB)</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Memory Used Avg (GB)</t>
+          <t>Memory Peak (GB)</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Memory Peak (GB)</t>
+          <t>CPU Util Avg %</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>CPU Util Avg %</t>
+          <t>CPU Util Peak %</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>CPU Util Peak %</t>
+          <t>Memory Util Avg %</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>Memory Util Avg %</t>
+          <t>Memory Util Peak %</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>Memory Util Peak %</t>
+          <t>Network In Avg (MB/s)</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Network In Peak (MB/s)</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Network In Peak Time</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Network Out Avg (MB/s)</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Network Out Peak (MB/s)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Network Out Peak Time</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Packets In Avg (count)</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Packets In Peak (count)</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Packets In Peak Time</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Packets Out Avg (count)</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Packets Out Peak (count)</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Packets Out Peak Time</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -761,28 +840,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>i-00cdafbb4615ca7fe</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>i-0b657e550bec4e711</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.301258</v>
+      </c>
       <c r="C2" t="n">
-        <v>0.055182</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.4965</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-04-23T16:35:00Z</t>
-        </is>
+        <v>1.852333</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>15.06290142670661</v>
       </c>
       <c r="I2" t="n">
-        <v>2.759103887420183</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24.825</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>92.61666666666667</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01113898881276448</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4974636427561442</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001289985201093886</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.00158900949690077</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-04-21T06:05:00Z</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>29683.82666666667</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1227311</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>17449.72666666667</v>
+      </c>
+      <c r="V2" t="n">
+        <v>57453</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -791,28 +913,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>i-011ba66691a9d53ba</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>i-0e688a8ecc5d1870d</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.199007</v>
+      </c>
       <c r="C3" t="n">
-        <v>0.055683</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.681833</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-04-21T06:35:00Z</t>
-        </is>
+        <v>3.1248</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4.97518730374247</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7841717914637</v>
-      </c>
-      <c r="J3" t="n">
-        <v>34.09166666666666</v>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>78.12</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.006620668955202456</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2338584706518385</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.001168845164334332</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.002041775650448269</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>24135.78666666667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>616086</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>17567.57333333333</v>
+      </c>
+      <c r="V3" t="n">
+        <v>69673</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -824,25 +989,68 @@
           <t>i-0178402b84983b5d4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0.184404</v>
+      </c>
       <c r="C4" t="n">
-        <v>0.183404</v>
-      </c>
-      <c r="D4" t="n">
         <v>1.401167</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-04-20T05:35:00Z</t>
-        </is>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-20T05:05:00Z</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>9.220215078499798</v>
       </c>
       <c r="I4" t="n">
-        <v>9.170192153538592</v>
-      </c>
-      <c r="J4" t="n">
         <v>70.05833333333334</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0.003815891420265909</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3591825678613451</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0009565424076234451</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.001602122518751356</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>14867.91919191919</v>
+      </c>
+      <c r="S4" t="n">
+        <v>796932</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>10426.17171717172</v>
+      </c>
+      <c r="V4" t="n">
+        <v>74918</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -851,28 +1059,71 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>i-0363f506ac77a647d</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>i-0a100856b64c3798a</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.059383</v>
+      </c>
       <c r="C5" t="n">
-        <v>0.060923</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.163833</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-04-22T10:35:00Z</t>
-        </is>
+        <v>1.227</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-22T07:05:00Z</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2.969140592885132</v>
       </c>
       <c r="I5" t="n">
-        <v>3.046150707630904</v>
-      </c>
-      <c r="J5" t="n">
-        <v>58.19166666666666</v>
-      </c>
-      <c r="M5" t="inlineStr">
+        <v>61.35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.002100205655608858</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1506482150819566</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-04-22T07:05:00Z</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0008509802037761325</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0009539201524522569</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-04-22T10:05:00Z</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>11531.55357142857</v>
+      </c>
+      <c r="S5" t="n">
+        <v>390942</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-04-22T07:05:00Z</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>9421.9375</v>
+      </c>
+      <c r="V5" t="n">
+        <v>42381</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-04-22T07:05:00Z</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -881,28 +1132,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>i-0a100856b64c3798a</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>i-0363f506ac77a647d</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.061233</v>
+      </c>
       <c r="C6" t="n">
-        <v>0.05818</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.227</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-04-22T07:35:00Z</t>
-        </is>
+        <v>1.163833</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-22T10:05:00Z</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3.061645330312299</v>
       </c>
       <c r="I6" t="n">
-        <v>2.909007716319793</v>
-      </c>
-      <c r="J6" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>58.19166666666666</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.00639676972109862</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.151606510480245</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-04-22T11:05:00Z</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001027651977057409</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.001715474923451742</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-04-22T11:05:00Z</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>15914.99090909091</v>
+      </c>
+      <c r="S6" t="n">
+        <v>244727</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-04-22T09:05:00Z</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>12240.92727272727</v>
+      </c>
+      <c r="V6" t="n">
+        <v>30625</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-04-22T11:05:00Z</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -911,28 +1205,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>i-0b657e550bec4e711</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>i-0cd0668d7e991cf99</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.444276</v>
+      </c>
       <c r="C7" t="n">
-        <v>0.296395</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.852333</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-04-20T17:35:00Z</t>
-        </is>
+        <v>8.345333</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2.776724997018213</v>
       </c>
       <c r="I7" t="n">
-        <v>14.8197274688406</v>
-      </c>
-      <c r="J7" t="n">
-        <v>92.61666666666667</v>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>52.15833333333333</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03130105725308727</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.016967899004618</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.006663564626884246</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.01583289729224311</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:05:00Z</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>137550.9898989899</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1508667</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>94839.83838383839</v>
+      </c>
+      <c r="V7" t="n">
+        <v>151013</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -941,28 +1278,71 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>i-0cd0668d7e991cf99</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>i-0f64d4949d506e2c3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.051804</v>
+      </c>
       <c r="C8" t="n">
-        <v>0.432699</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8.345333</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-04-18T17:35:00Z</t>
-        </is>
+        <v>0.740167</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-23T14:05:00Z</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2.590179416993295</v>
       </c>
       <c r="I8" t="n">
-        <v>2.704367439054244</v>
-      </c>
-      <c r="J8" t="n">
-        <v>52.15833333333333</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>37.00833333333333</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.004315300713841317</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0317712836795383</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-04-23T14:05:00Z</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0.002113807126164273</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.004070574177636041</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-04-23T18:05:00Z</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>48941.76543209876</v>
+      </c>
+      <c r="S8" t="n">
+        <v>106449</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-04-23T14:05:00Z</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>33952.01234567901</v>
+      </c>
+      <c r="V8" t="n">
+        <v>36622</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-04-25T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -971,28 +1351,71 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>i-0e688a8ecc5d1870d</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>i-011ba66691a9d53ba</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.055644</v>
+      </c>
       <c r="C9" t="n">
-        <v>0.192484</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.1248</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-04-21T17:35:00Z</t>
-        </is>
+        <v>0.681833</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-21T07:05:00Z</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2.782188613574404</v>
       </c>
       <c r="I9" t="n">
-        <v>4.812107705506984</v>
-      </c>
-      <c r="J9" t="n">
-        <v>78.12</v>
-      </c>
-      <c r="M9" t="inlineStr">
+        <v>34.09166666666666</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002660321594244424</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1002754577000936</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-04-21T05:05:00Z</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001250621600619453</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.004521430068545871</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-04-24T00:05:00Z</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>12912.26811594203</v>
+      </c>
+      <c r="S9" t="n">
+        <v>256131</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-04-21T05:05:00Z</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>11552.98550724638</v>
+      </c>
+      <c r="V9" t="n">
+        <v>20753</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-04-21T05:05:00Z</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -1001,28 +1424,71 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>i-0f64d4949d506e2c3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>i-00cdafbb4615ca7fe</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.05542</v>
+      </c>
       <c r="C10" t="n">
-        <v>0.052892</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.740167</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-04-23T13:35:00Z</t>
-        </is>
+        <v>0.4965</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-23T16:05:00Z</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2.771020720037356</v>
       </c>
       <c r="I10" t="n">
-        <v>2.644581149378913</v>
-      </c>
-      <c r="J10" t="n">
-        <v>37.00833333333333</v>
-      </c>
-      <c r="M10" t="inlineStr">
+        <v>24.825</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001391075183905965</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.05140464305877686</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-04-23T16:05:00Z</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0009016650001375652</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0009461651908026801</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-04-24T03:05:00Z</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>9670.012658227848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>135979</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-04-23T16:05:00Z</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>8835.860759493671</v>
+      </c>
+      <c r="V10" t="n">
+        <v>14334</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-04-23T16:05:00Z</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>Historical: EC2 / CloudWatch</t>
         </is>
@@ -1039,7 +1505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1573,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1138,7 +1604,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1169,7 +1635,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1200,7 +1666,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1231,7 +1697,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1262,7 +1728,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1289,11 +1755,11 @@
         <v>0.002</v>
       </c>
       <c r="D8" t="n">
-        <v>0.306641</v>
+        <v>0.307617</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1324,7 +1790,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1355,7 +1821,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1386,7 +1852,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1417,7 +1883,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1444,11 +1910,11 @@
         <v>0.001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.308594</v>
+        <v>0.30957</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1479,7 +1945,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1510,7 +1976,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1537,11 +2003,11 @@
         <v>0.002</v>
       </c>
       <c r="D16" t="n">
-        <v>0.385742</v>
+        <v>0.386719</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1572,7 +2038,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1603,7 +2069,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1627,14 +2093,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="D19" t="n">
         <v>0.321289</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1665,7 +2131,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1696,7 +2162,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1727,7 +2193,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1758,7 +2224,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1789,7 +2255,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1820,7 +2286,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1844,14 +2310,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="D26" t="n">
-        <v>1.498047</v>
+        <v>1.499023</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1882,7 +2348,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1913,13 +2379,44 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>keycloak</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>keycloak-58df4c66dd-s5bqk</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.487305</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>22:07:57</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
@@ -1931,271 +2428,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Top Nodes By Snapshot Utilisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Node</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Avg CPU Used</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Peak CPU</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Avg Mem Used</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Peak Mem</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Peak CPU Util %</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Peak Mem Util %</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Peak Observed Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>i-0b657e550bec4e711</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.296395</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.852333</v>
-      </c>
-      <c r="F3" t="n">
-        <v>92.61666666666667</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-04-20T17:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>i-0e688a8ecc5d1870d</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.192484</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.1248</v>
-      </c>
-      <c r="F4" t="n">
-        <v>78.12</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-04-21T17:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>i-0178402b84983b5d4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.183404</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.401167</v>
-      </c>
-      <c r="F5" t="n">
-        <v>70.05833333333334</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-04-20T05:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>i-0a100856b64c3798a</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.05818</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.227</v>
-      </c>
-      <c r="F6" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-04-22T07:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>i-0363f506ac77a647d</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.060923</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.163833</v>
-      </c>
-      <c r="F7" t="n">
-        <v>58.19166666666666</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-04-22T10:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>i-0cd0668d7e991cf99</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.432699</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8.345333</v>
-      </c>
-      <c r="F8" t="n">
-        <v>52.15833333333333</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-04-18T17:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>i-0f64d4949d506e2c3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.052892</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.740167</v>
-      </c>
-      <c r="F9" t="n">
-        <v>37.00833333333333</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-04-23T13:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>i-011ba66691a9d53ba</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.055683</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.681833</v>
-      </c>
-      <c r="F10" t="n">
-        <v>34.09166666666666</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-04-21T06:35:00Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>i-00cdafbb4615ca7fe</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.055182</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.4965</v>
-      </c>
-      <c r="F11" t="n">
-        <v>24.825</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-04-23T16:35:00Z</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2277,7 +2509,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -2296,14 +2528,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="D5" t="n">
-        <v>1.498047</v>
+        <v>1.499023</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2329,7 +2561,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -2339,23 +2571,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dgh-ns</t>
+          <t>keycloak</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
+          <t>keycloak-58df4c66dd-s5bqk</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.420898</v>
+        <v>0.487305</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2370,18 +2602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ims-udm-service-6b56656f56-9wk8d</t>
+          <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0.001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.392578</v>
+        <v>0.420898</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2396,18 +2628,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ims-user-profile-service-5d6bdcfcdc-l2lmj</t>
+          <t>ims-udm-service-6b56656f56-9wk8d</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0.001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.388672</v>
+        <v>0.392578</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2422,18 +2654,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ims-master-data-service-7568c4c56b-6srt6</t>
+          <t>ims-user-profile-service-5d6bdcfcdc-l2lmj</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.385742</v>
+        <v>0.388672</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2448,18 +2680,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
+          <t>ims-master-data-service-7568c4c56b-6srt6</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="D11" t="n">
-        <v>0.370117</v>
+        <v>0.386719</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2474,18 +2706,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
+          <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0.001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.360352</v>
+        <v>0.370117</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2500,18 +2732,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ims-user-login-service-7b4bdb4975-hb8d4</t>
+          <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0.001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.337891</v>
+        <v>0.360352</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20:36:15</t>
+          <t>22:07:57</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2525,82 +2757,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Namespace</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>HPA</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CPU target</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Memory target</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>MinPods</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>MaxPods</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Replicas</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Snapshot Time</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/cluster_infra_report.xlsx
+++ b/cluster_infra_report.xlsx
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +79,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,14 +448,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28.18421052631579" customWidth="1" min="1" max="1"/>
+    <col width="17.40789473684211" customWidth="1" min="2" max="2"/>
+    <col width="5.802631578947368" customWidth="1" min="3" max="3"/>
+    <col width="18.23684210526316" customWidth="1" min="4" max="4"/>
+    <col width="24.03947368421053" customWidth="1" min="5" max="5"/>
+    <col width="10.77631578947368" customWidth="1" min="6" max="6"/>
+    <col width="10.77631578947368" customWidth="1" min="7" max="7"/>
+    <col width="10.77631578947368" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,7 +501,7 @@
           <t>Report Period Start (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
@@ -507,7 +513,7 @@
           <t>Report Period End (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
@@ -519,7 +525,7 @@
           <t>Timezone</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>UTC</t>
         </is>
@@ -531,7 +537,7 @@
           <t>Kubernetes version</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>v1.33.8-eks-f69f56f</t>
         </is>
@@ -543,15 +549,15 @@
           <t>Node group size</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>nodes</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Historical EC2 / CloudWatch</t>
         </is>
@@ -572,20 +578,20 @@
           <t>Highest node CPU usage</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-20T17:05:00Z</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:45:00Z</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>i-0b657e550bec4e711 at 92%</t>
         </is>
@@ -597,18 +603,18 @@
           <t>Highest node memory usage</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>i-0a100856b64c3798a at 100%</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>i-0a100856b64c3798a at 101%</t>
         </is>
       </c>
     </row>
@@ -618,15 +624,15 @@
           <t>Average node CPU usage</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="4" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Historical EC2 / CloudWatch</t>
         </is>
@@ -638,15 +644,15 @@
           <t>Average node memory usage</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="4" t="n">
         <v>73.44</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Historical EC2 / CloudWatch</t>
         </is>
@@ -658,15 +664,15 @@
           <t>Nodes above 80% CPU</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Historical EC2 / CloudWatch</t>
         </is>
@@ -689,15 +695,15 @@
   <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="16.13414634146341" customWidth="1" min="1" max="1"/>
+    <col width="16.90243902439024" customWidth="1" min="2" max="2"/>
+    <col width="13.82926829268293" customWidth="1" min="3" max="3"/>
+    <col width="16.90243902439024" customWidth="1" min="4" max="4"/>
+    <col width="16.13414634146341" customWidth="1" min="5" max="5"/>
+    <col width="16.90243902439024" customWidth="1" min="6" max="6"/>
+    <col width="13.82926829268293" customWidth="1" min="7" max="7"/>
+    <col width="15.36585365853659" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
@@ -712,7 +718,7 @@
     <col width="25" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="23" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -838,70 +844,70 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>i-0b657e550bec4e711</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.301258</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="4" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>1.852333</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-20T17:05:00Z</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>15.06290142670661</v>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:45:00Z</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>14.81200747885071</v>
       </c>
       <c r="I2" t="n">
         <v>92.61666666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01113898881276448</v>
+        <v>0.01117023107210795</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4974636427561442</v>
+        <v>0.5024426817893982</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:05:00Z</t>
+          <t>2026-04-20T17:45:00Z</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.001289985201093886</v>
+        <v>0.001295926343070136</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00158900949690077</v>
+        <v>0.002231365309821235</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-04-21T06:05:00Z</t>
+          <t>2026-04-20T17:45:00Z</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>29683.82666666667</v>
+        <v>29775.83333333333</v>
       </c>
       <c r="S2" t="n">
-        <v>1227311</v>
+        <v>1241181</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:05:00Z</t>
+          <t>2026-04-20T17:45:00Z</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>17449.72666666667</v>
+        <v>17528.21333333333</v>
       </c>
       <c r="V2" t="n">
-        <v>57453</v>
+        <v>69017</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:05:00Z</t>
+          <t>2026-04-20T17:45:00Z</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -911,70 +917,70 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>i-0e688a8ecc5d1870d</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.199007</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="4" t="n">
+        <v>0.193718</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>3.1248</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-21T17:05:00Z</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4.97518730374247</v>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21T17:45:00Z</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>4.842938825071783</v>
       </c>
       <c r="I3" t="n">
         <v>78.12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006620668955202456</v>
+        <v>0.006637285562797829</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2338584706518385</v>
+        <v>0.234450253645579</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:05:00Z</t>
+          <t>2026-04-21T17:45:00Z</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.001168845164334332</v>
+        <v>0.001174611111040469</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002041775650448269</v>
+        <v>0.00216315507888794</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:05:00Z</t>
+          <t>2026-04-21T17:45:00Z</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>24135.78666666667</v>
+        <v>24247.45333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>616086</v>
+        <v>619517</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:05:00Z</t>
+          <t>2026-04-21T17:45:00Z</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>17567.57333333333</v>
+        <v>17664.31333333333</v>
       </c>
       <c r="V3" t="n">
-        <v>69673</v>
+        <v>72057</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:05:00Z</t>
+          <t>2026-04-21T17:45:00Z</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -984,70 +990,70 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>i-0178402b84983b5d4</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.184404</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>0.184045</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1.401167</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-20T05:05:00Z</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>9.220215078499798</v>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20T04:45:00Z</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>9.202271535807066</v>
       </c>
       <c r="I4" t="n">
         <v>70.05833333333334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003815891420265909</v>
+        <v>0.003819418829833351</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3591825678613451</v>
+        <v>0.3598293595843845</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.0009565424076234451</v>
+        <v>0.0009598318294242576</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001602122518751356</v>
+        <v>0.002202074527740479</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>14867.91919191919</v>
+        <v>14900.5404040404</v>
       </c>
       <c r="S4" t="n">
-        <v>796932</v>
+        <v>803046</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>10426.17171717172</v>
+        <v>10460.94444444445</v>
       </c>
       <c r="V4" t="n">
-        <v>74918</v>
+        <v>81112</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1057,70 +1063,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>i-0a100856b64c3798a</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.059383</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" s="4" t="n">
+        <v>0.058207</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1.227</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-22T07:05:00Z</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>2.969140592885132</v>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22T07:45:00Z</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2.910345088182749</v>
       </c>
       <c r="I5" t="n">
         <v>61.35</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002100205655608858</v>
+        <v>0.002105103303042669</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1506482150819566</v>
+        <v>0.1511395419968499</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:05:00Z</t>
+          <t>2026-04-22T07:45:00Z</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.0008509802037761325</v>
+        <v>0.0008563877642154693</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0009539201524522569</v>
+        <v>0.001469386683570014</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-04-22T10:05:00Z</t>
+          <t>2026-04-22T07:45:00Z</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>11531.55357142857</v>
+        <v>11582.72321428571</v>
       </c>
       <c r="S5" t="n">
-        <v>390942</v>
+        <v>396311</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:05:00Z</t>
+          <t>2026-04-22T07:45:00Z</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>9421.9375</v>
+        <v>9479.223214285714</v>
       </c>
       <c r="V5" t="n">
-        <v>42381</v>
+        <v>48430</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:05:00Z</t>
+          <t>2026-04-22T07:45:00Z</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1130,70 +1136,70 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>i-0363f506ac77a647d</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.061233</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" s="4" t="n">
+        <v>0.061364</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>1.163833</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-22T10:05:00Z</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3.061645330312299</v>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22T10:45:00Z</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>3.068194057186596</v>
       </c>
       <c r="I6" t="n">
         <v>58.19166666666666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00639676972109862</v>
+        <v>0.006404113456456348</v>
       </c>
       <c r="M6" t="n">
-        <v>0.151606510480245</v>
+        <v>0.2260492271847195</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-04-22T11:05:00Z</t>
+          <t>2026-04-22T10:45:00Z</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.001027651977057409</v>
+        <v>0.001034132466171727</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001715474923451742</v>
+        <v>0.001656428707970513</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-04-22T11:05:00Z</t>
+          <t>2026-04-22T10:45:00Z</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>15914.99090909091</v>
+        <v>15982.8</v>
       </c>
       <c r="S6" t="n">
-        <v>244727</v>
+        <v>267982</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-04-22T09:05:00Z</t>
+          <t>2026-04-22T09:45:00Z</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>12240.92727272727</v>
+        <v>12315.80909090909</v>
       </c>
       <c r="V6" t="n">
-        <v>30625</v>
+        <v>37277</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-04-22T11:05:00Z</t>
+          <t>2026-04-22T10:45:00Z</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1203,70 +1209,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>i-0cd0668d7e991cf99</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.444276</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="4" t="n">
+        <v>0.429799</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>8.345333</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-18T17:05:00Z</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2.776724997018213</v>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18T17:45:00Z</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>2.686245221870573</v>
       </c>
       <c r="I7" t="n">
         <v>52.15833333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03130105725308727</v>
+        <v>0.03134868211483982</v>
       </c>
       <c r="M7" t="n">
-        <v>1.016967899004618</v>
+        <v>1.025703057977888</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.006663564626884246</v>
+        <v>0.006684572823788849</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01583289729224311</v>
+        <v>0.01683397478527493</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-04-20T06:05:00Z</t>
+          <t>2026-04-20T05:45:00Z</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>137550.9898989899</v>
+        <v>137935.4191919192</v>
       </c>
       <c r="S7" t="n">
-        <v>1508667</v>
+        <v>1578067</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>94839.83838383839</v>
+        <v>95160.18686868687</v>
       </c>
       <c r="V7" t="n">
-        <v>151013</v>
+        <v>207212</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-04-18T17:05:00Z</t>
+          <t>2026-04-18T17:45:00Z</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1276,70 +1282,70 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>i-0f64d4949d506e2c3</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.051804</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" s="4" t="n">
+        <v>0.052176</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.740167</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-23T14:05:00Z</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2.590179416993295</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>2.608808913345478</v>
       </c>
       <c r="I8" t="n">
         <v>37.00833333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004315300713841317</v>
+        <v>0.004295286941657545</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0317712836795383</v>
+        <v>0.03039214081234402</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-04-23T14:05:00Z</t>
+          <t>2026-04-23T13:45:00Z</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.002113807126164273</v>
+        <v>0.002105093066931417</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004070574177636041</v>
+        <v>0.00554752614763048</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-04-23T18:05:00Z</t>
+          <t>2026-04-23T18:45:00Z</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>48941.76543209876</v>
+        <v>48749.64634146341</v>
       </c>
       <c r="S8" t="n">
-        <v>106449</v>
+        <v>89795</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-04-23T14:05:00Z</t>
+          <t>2026-04-23T13:45:00Z</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>33952.01234567901</v>
+        <v>33822.98780487805</v>
       </c>
       <c r="V8" t="n">
-        <v>36622</v>
+        <v>37595</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-04-25T17:05:00Z</t>
+          <t>2026-04-23T18:45:00Z</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1349,70 +1355,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>i-011ba66691a9d53ba</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.055644</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" s="4" t="n">
+        <v>0.055719</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.681833</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-21T07:05:00Z</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2.782188613574404</v>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2.7859544592543</v>
       </c>
       <c r="I9" t="n">
         <v>34.09166666666666</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002660321594244424</v>
+        <v>0.002645497966251023</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1002754577000936</v>
+        <v>0.1000318826569451</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-04-21T05:05:00Z</t>
+          <t>2026-04-21T04:45:00Z</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.001250621600619453</v>
+        <v>0.00124678622237403</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004521430068545871</v>
+        <v>0.004858788119422065</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-04-24T00:05:00Z</t>
+          <t>2026-04-23T23:45:00Z</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>12912.26811594203</v>
+        <v>12869.05035971223</v>
       </c>
       <c r="S9" t="n">
-        <v>256131</v>
+        <v>253456</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-04-21T05:05:00Z</t>
+          <t>2026-04-21T04:45:00Z</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>11552.98550724638</v>
+        <v>11526.02158273381</v>
       </c>
       <c r="V9" t="n">
-        <v>20753</v>
+        <v>18814</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-04-21T05:05:00Z</t>
+          <t>2026-04-21T17:45:00Z</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1422,70 +1428,70 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>i-00cdafbb4615ca7fe</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.05542</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="4" t="n">
+        <v>0.055109</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.4965</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-23T16:05:00Z</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2.771020720037356</v>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23T16:45:00Z</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2.755439003431746</v>
       </c>
       <c r="I10" t="n">
         <v>24.825</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001391075183905965</v>
+        <v>0.00139768865708728</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05140464305877686</v>
+        <v>0.05190634303622776</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:05:00Z</t>
+          <t>2026-04-23T16:45:00Z</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.0009016650001375652</v>
+        <v>0.0009096924229177912</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0009461651908026801</v>
+        <v>0.001015908718109131</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-04-24T03:05:00Z</t>
+          <t>2026-04-23T16:45:00Z</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>9670.012658227848</v>
+        <v>9740.405063291139</v>
       </c>
       <c r="S10" t="n">
-        <v>135979</v>
+        <v>141408</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:05:00Z</t>
+          <t>2026-04-23T16:45:00Z</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>8835.860759493671</v>
+        <v>8912.126582278481</v>
       </c>
       <c r="V10" t="n">
-        <v>14334</v>
+        <v>20226</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:05:00Z</t>
+          <t>2026-04-23T16:45:00Z</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1505,16 +1511,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8.555555555555555" customWidth="1" min="1" max="1"/>
+    <col width="39.66666666666666" customWidth="1" min="2" max="2"/>
+    <col width="10.11111111111111" customWidth="1" min="3" max="3"/>
+    <col width="16.33333333333333" customWidth="1" min="4" max="4"/>
+    <col width="11.66666666666667" customWidth="1" min="5" max="5"/>
+    <col width="7.777777777777778" customWidth="1" min="6" max="6"/>
+    <col width="21.77777777777778" customWidth="1" min="7" max="7"/>
+    <col width="10.11111111111111" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1555,868 +1562,868 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>elasticsearch-cluster-es-default-0</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="4" t="n">
         <v>0.007</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="4" t="n">
         <v>1.582031</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>frontend-service-64dbb5d6c9-8m5f2</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>0.013672</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ims-admin-service-6c97cc44b7-tmfhb</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.254883</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ims-audit-service-59cbc79846-9nhqm</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.238281</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ims-compliance-service-797b7b4b7d-f57g2</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.292969</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ims-correspondence-service-d887b48d9-2xhxx</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.324219</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ims-eml-service-6b568f9864-4lmf2</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.308594</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ims-excel-service-665dd589cf-lrb6h</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.324219</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="D9" s="4" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ims-eml-service-6b568f9864-4lmf2</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ims-facts-sheet-service-855dc8d689-6vfhf</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.291016</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ims-financial-service-7f65f7f79c-62l58</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.588867</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ims-integration-service-5f46dbcd78-wxbbm</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.292969</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ims-inventory-track-service-5dffdf6cdb-4jxql</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.310547</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ims-keycloak-service-6f897b454c-9w9kt</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.292969</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ims-logical-doc-service-588d85ccdd-6mdtd</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.264648</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ims-master-data-service-7568c4c56b-6srt6</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.307617</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="D16" s="4" t="n">
+        <v>0.386719</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ims-excel-service-665dd589cf-lrb6h</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ims-miscellaneous-service-69fbfbbf57-ncgfn</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.24707</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D17" s="4" t="n">
+        <v>0.279297</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ims-facts-sheet-service-855dc8d689-6vfhf</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ims-pdf-service-5ccdc6548d-mx2s9</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.291016</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D18" s="4" t="n">
+        <v>0.208008</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ims-financial-service-7f65f7f79c-62l58</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ims-site-restoration-service-745f8fb5bc-msb9q</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.588867</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="D19" s="4" t="n">
+        <v>0.321289</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ims-integration-service-5f46dbcd78-wxbbm</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.292969</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="D20" s="4" t="n">
+        <v>0.370117</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ims-inventory-track-service-5dffdf6cdb-4jxql</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ims-udm-service-6b56656f56-9wk8d</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.30957</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D21" s="4" t="n">
+        <v>0.392578</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ims-keycloak-service-6f897b454c-9w9kt</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ims-user-login-service-7b4bdb4975-hb8d4</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.292969</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="D22" s="4" t="n">
+        <v>0.337891</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ims-logical-doc-service-588d85ccdd-6mdtd</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ims-user-profile-service-5d6bdcfcdc-l2lmj</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.264648</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="D23" s="4" t="n">
+        <v>0.388672</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ims-master-data-service-7568c4c56b-6srt6</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.386719</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.360352</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ims-miscellaneous-service-69fbfbbf57-ncgfn</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.279297</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="D25" s="4" t="n">
+        <v>0.420898</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ims-pdf-service-5ccdc6548d-mx2s9</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>logstash-ls-0</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1.498047</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot: kubectl top pods</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>my-memcached-64c67cf489-4lch9</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.208008</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="D27" s="4" t="n">
+        <v>0.003906</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ims-site-restoration-service-745f8fb5bc-msb9q</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.321289</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>zipkin-56bb685bdc-rff4f</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0.158203</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>keycloak</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>keycloak-58df4c66dd-s5bqk</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.370117</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ims-udm-service-6b56656f56-9wk8d</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.392578</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ims-user-login-service-7b4bdb4975-hb8d4</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.337891</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ims-user-profile-service-5d6bdcfcdc-l2lmj</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.388672</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.360352</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.420898</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>logstash-ls-0</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.499023</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>my-memcached-64c67cf489-4lch9</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.003906</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>zipkin-56bb685bdc-rff4f</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.158203</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Snapshot: kubectl top pods</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>keycloak</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>keycloak-58df4c66dd-s5bqk</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.487305</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>Snapshot: kubectl top pods</t>
         </is>
@@ -2433,15 +2440,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="36.28272251308901" customWidth="1" min="1" max="1"/>
+    <col width="33.64397905759162" customWidth="1" min="2" max="2"/>
+    <col width="8.575916230366493" customWidth="1" min="3" max="3"/>
+    <col width="13.85340314136126" customWidth="1" min="4" max="4"/>
+    <col width="9.895287958115183" customWidth="1" min="5" max="5"/>
+    <col width="6.596858638743456" customWidth="1" min="6" max="6"/>
+    <col width="8.575916230366493" customWidth="1" min="7" max="7"/>
+    <col width="8.575916230366493" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2491,262 +2500,262 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>elasticsearch-cluster-es-default-0</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="4" t="n">
         <v>0.007</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>1.582031</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>logstash-ls-0</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.007</v>
       </c>
-      <c r="D5" t="n">
-        <v>1.499023</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5" s="4" t="n">
+        <v>1.498047</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ims-financial-service-7f65f7f79c-62l58</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.588867</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>keycloak</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>keycloak-58df4c66dd-s5bqk</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.487305</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.420898</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ims-udm-service-6b56656f56-9wk8d</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.392578</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ims-user-profile-service-5d6bdcfcdc-l2lmj</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.388672</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ims-master-data-service-7568c4c56b-6srt6</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="4" t="n">
         <v>0.002</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.386719</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.370117</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.360352</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>22:07:57</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>22:49:08</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/cluster_infra_report.xlsx
+++ b/cluster_infra_report.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T17:45:00Z</t>
+          <t>2026-04-20T17:05:00Z</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>i-0a100856b64c3798a at 101%</t>
+          <t>i-0a100856b64c3798a at 100%</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>73.44</v>
+        <v>75.89</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -850,64 +850,64 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0.29624</v>
+        <v>0.298596</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1.852333</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T17:45:00Z</t>
+          <t>2026-04-20T17:05:00Z</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>14.81200747885071</v>
+        <v>14.92979612601127</v>
       </c>
       <c r="I2" t="n">
         <v>92.61666666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01117023107210795</v>
+        <v>0.01094678843856617</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5024426817893982</v>
+        <v>0.4974636427561442</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:45:00Z</t>
+          <t>2026-04-20T17:05:00Z</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.001295926343070136</v>
+        <v>0.001290303643342036</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002231365309821235</v>
+        <v>0.00158900949690077</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:45:00Z</t>
+          <t>2026-04-21T06:05:00Z</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>29775.83333333333</v>
+        <v>29258.4076433121</v>
       </c>
       <c r="S2" t="n">
-        <v>1241181</v>
+        <v>1227311</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:45:00Z</t>
+          <t>2026-04-20T17:05:00Z</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>17528.21333333333</v>
+        <v>17438.00636942675</v>
       </c>
       <c r="V2" t="n">
-        <v>69017</v>
+        <v>57453</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-04-20T17:45:00Z</t>
+          <t>2026-04-20T17:05:00Z</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -923,64 +923,64 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0.193718</v>
+        <v>0.199746</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>3.1248</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21T17:45:00Z</t>
+          <t>2026-04-21T17:05:00Z</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.842938825071783</v>
+        <v>4.993656659626565</v>
       </c>
       <c r="I3" t="n">
         <v>78.12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006637285562797829</v>
+        <v>0.006487174405329462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.234450253645579</v>
+        <v>0.2338584706518385</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:45:00Z</t>
+          <t>2026-04-21T17:05:00Z</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.001174611111040469</v>
+        <v>0.001172493938343456</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00216315507888794</v>
+        <v>0.002041775650448269</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:45:00Z</t>
+          <t>2026-04-21T17:05:00Z</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>24247.45333333333</v>
+        <v>24149.93630573248</v>
       </c>
       <c r="S3" t="n">
-        <v>619517</v>
+        <v>616086</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:45:00Z</t>
+          <t>2026-04-21T17:05:00Z</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>17664.31333333333</v>
+        <v>17726.40127388535</v>
       </c>
       <c r="V3" t="n">
-        <v>72057</v>
+        <v>69673</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-04-21T17:45:00Z</t>
+          <t>2026-04-21T17:05:00Z</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -996,64 +996,64 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.184045</v>
+        <v>0.188145</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1.401167</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20T04:45:00Z</t>
+          <t>2026-04-20T05:05:00Z</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>9.202271535807066</v>
+        <v>9.407262589760057</v>
       </c>
       <c r="I4" t="n">
         <v>70.05833333333334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003819418829833351</v>
+        <v>0.003720660262637668</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3598293595843845</v>
+        <v>0.3591825678613451</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.0009598318294242576</v>
+        <v>0.0009563868943914812</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002202074527740479</v>
+        <v>0.001602122518751356</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>14900.5404040404</v>
+        <v>14684.13658536585</v>
       </c>
       <c r="S4" t="n">
-        <v>803046</v>
+        <v>796932</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>10460.94444444445</v>
+        <v>10415.92195121951</v>
       </c>
       <c r="V4" t="n">
-        <v>81112</v>
+        <v>74918</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1069,64 +1069,64 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.058207</v>
+        <v>0.05937</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.227</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22T07:45:00Z</t>
+          <t>2026-04-22T07:05:00Z</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2.910345088182749</v>
+        <v>2.968488537391148</v>
       </c>
       <c r="I5" t="n">
         <v>61.35</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002105103303042669</v>
+        <v>0.002022657781755891</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1511395419968499</v>
+        <v>0.1506482150819566</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:45:00Z</t>
+          <t>2026-04-22T07:05:00Z</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.0008563877642154693</v>
+        <v>0.0008515044776888009</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001469386683570014</v>
+        <v>0.0009539201524522569</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:45:00Z</t>
+          <t>2026-04-22T10:05:00Z</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>11582.72321428571</v>
+        <v>11338.65546218487</v>
       </c>
       <c r="S5" t="n">
-        <v>396311</v>
+        <v>390942</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:45:00Z</t>
+          <t>2026-04-22T07:05:00Z</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>9479.223214285714</v>
+        <v>9413.941176470587</v>
       </c>
       <c r="V5" t="n">
-        <v>48430</v>
+        <v>42381</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-04-22T07:45:00Z</t>
+          <t>2026-04-22T07:05:00Z</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1142,64 +1142,64 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.061364</v>
+        <v>0.062276</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.163833</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22T10:45:00Z</t>
+          <t>2026-04-22T10:05:00Z</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.068194057186596</v>
+        <v>3.113788107321155</v>
       </c>
       <c r="I6" t="n">
         <v>58.19166666666666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006404113456456348</v>
+        <v>0.006083760173232467</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2260492271847195</v>
+        <v>0.151606510480245</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-04-22T10:45:00Z</t>
+          <t>2026-04-22T11:05:00Z</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.001034132466171727</v>
+        <v>0.001028728774922979</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001656428707970513</v>
+        <v>0.001715474923451742</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-04-22T10:45:00Z</t>
+          <t>2026-04-22T11:05:00Z</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>15982.8</v>
+        <v>15611.86324786325</v>
       </c>
       <c r="S6" t="n">
-        <v>267982</v>
+        <v>244727</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-04-22T09:45:00Z</t>
+          <t>2026-04-22T09:05:00Z</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>12315.80909090909</v>
+        <v>12227.34188034188</v>
       </c>
       <c r="V6" t="n">
-        <v>37277</v>
+        <v>30625</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-04-22T10:45:00Z</t>
+          <t>2026-04-22T11:05:00Z</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1215,64 +1215,64 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.429799</v>
+        <v>0.447423</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>8.345333</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.686245221870573</v>
+        <v>2.796392110941169</v>
       </c>
       <c r="I7" t="n">
         <v>52.15833333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03134868211483982</v>
+        <v>0.03070342919367762</v>
       </c>
       <c r="M7" t="n">
-        <v>1.025703057977888</v>
+        <v>1.016967899004618</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.006684572823788849</v>
+        <v>0.006649319137014994</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01683397478527493</v>
+        <v>0.01583289729224311</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-04-20T05:45:00Z</t>
+          <t>2026-04-20T06:05:00Z</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>137935.4191919192</v>
+        <v>136655.7219512195</v>
       </c>
       <c r="S7" t="n">
-        <v>1578067</v>
+        <v>1508667</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>95160.18686868687</v>
+        <v>94778.48292682927</v>
       </c>
       <c r="V7" t="n">
-        <v>207212</v>
+        <v>151013</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-04-18T17:45:00Z</t>
+          <t>2026-04-18T17:05:00Z</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1288,64 +1288,64 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.052176</v>
+        <v>0.051839</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.740167</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23T13:45:00Z</t>
+          <t>2026-04-23T14:05:00Z</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.608808913345478</v>
+        <v>2.591954790098145</v>
       </c>
       <c r="I8" t="n">
         <v>37.00833333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004295286941657545</v>
+        <v>0.00429863424915256</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03039214081234402</v>
+        <v>0.0317712836795383</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-04-23T13:45:00Z</t>
+          <t>2026-04-23T14:05:00Z</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.002105093066931417</v>
+        <v>0.002122715407549733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00554752614763048</v>
+        <v>0.004070574177636041</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-04-23T18:45:00Z</t>
+          <t>2026-04-23T18:05:00Z</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>48749.64634146341</v>
+        <v>48943.21590909091</v>
       </c>
       <c r="S8" t="n">
-        <v>89795</v>
+        <v>106449</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-04-23T13:45:00Z</t>
+          <t>2026-04-23T14:05:00Z</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>33822.98780487805</v>
+        <v>33999.21590909091</v>
       </c>
       <c r="V8" t="n">
-        <v>37595</v>
+        <v>36622</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-04-23T18:45:00Z</t>
+          <t>2026-04-25T17:05:00Z</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0.055719</v>
+        <v>0.055607</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.681833</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21T06:45:00Z</t>
+          <t>2026-04-21T07:05:00Z</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.7859544592543</v>
+        <v>2.780369354834797</v>
       </c>
       <c r="I9" t="n">
         <v>34.09166666666666</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002645497966251023</v>
+        <v>0.002574209317393687</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1000318826569451</v>
+        <v>0.1002754577000936</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:00Z</t>
+          <t>2026-04-21T05:05:00Z</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.00124678622237403</v>
+        <v>0.001241262172830516</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004858788119422065</v>
+        <v>0.004521430068545871</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-04-23T23:45:00Z</t>
+          <t>2026-04-24T00:05:00Z</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>12869.05035971223</v>
+        <v>12778.60689655172</v>
       </c>
       <c r="S9" t="n">
-        <v>253456</v>
+        <v>256131</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:00Z</t>
+          <t>2026-04-21T05:05:00Z</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>11526.02158273381</v>
+        <v>11550.46896551724</v>
       </c>
       <c r="V9" t="n">
-        <v>18814</v>
+        <v>20753</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-04-21T17:45:00Z</t>
+          <t>2026-04-21T05:05:00Z</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1434,64 +1434,64 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.055109</v>
+        <v>0.055374</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.4965</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23T16:45:00Z</t>
+          <t>2026-04-23T16:05:00Z</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.755439003431746</v>
+        <v>2.768700881067907</v>
       </c>
       <c r="I10" t="n">
         <v>24.825</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00139768865708728</v>
+        <v>0.00134039809229454</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05190634303622776</v>
+        <v>0.05140464305877686</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:45:00Z</t>
+          <t>2026-04-23T16:05:00Z</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.0009096924229177912</v>
+        <v>0.0009031303692849723</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001015908718109131</v>
+        <v>0.0009461651908026801</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:45:00Z</t>
+          <t>2026-04-24T03:05:00Z</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>9740.405063291139</v>
+        <v>9547.941860465116</v>
       </c>
       <c r="S10" t="n">
-        <v>141408</v>
+        <v>135979</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:45:00Z</t>
+          <t>2026-04-23T16:05:00Z</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>8912.126582278481</v>
+        <v>8838.848837209302</v>
       </c>
       <c r="V10" t="n">
-        <v>20226</v>
+        <v>14334</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-04-23T16:45:00Z</t>
+          <t>2026-04-23T16:05:00Z</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1573,14 +1573,14 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>1.582031</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -1700,11 +1700,11 @@
         <v>0.001</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.292969</v>
+        <v>0.293945</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -1728,14 +1728,14 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0.324219</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
@@ -1762,11 +1762,11 @@
         <v>0.002</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.308594</v>
+        <v>0.30957</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -1793,11 +1793,11 @@
         <v>0.001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.24707</v>
+        <v>0.248047</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -1824,11 +1824,11 @@
         <v>0.001</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.291016</v>
+        <v>0.291992</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -1979,11 +1979,11 @@
         <v>0.001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.264648</v>
+        <v>0.265625</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -2010,11 +2010,11 @@
         <v>0.002</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.386719</v>
+        <v>0.388672</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -2041,11 +2041,11 @@
         <v>0.001</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.279297</v>
+        <v>0.286133</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -2165,11 +2165,11 @@
         <v>0.001</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.392578</v>
+        <v>0.393555</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
@@ -2227,11 +2227,11 @@
         <v>0.001</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.388672</v>
+        <v>0.387695</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
@@ -2258,11 +2258,11 @@
         <v>0.001</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.360352</v>
+        <v>0.361328</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
@@ -2286,14 +2286,14 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>0.420898</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -2317,14 +2317,14 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.498047</v>
+        <v>1.499023</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -2440,17 +2440,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36.28272251308901" customWidth="1" min="1" max="1"/>
-    <col width="33.64397905759162" customWidth="1" min="2" max="2"/>
-    <col width="8.575916230366493" customWidth="1" min="3" max="3"/>
-    <col width="13.85340314136126" customWidth="1" min="4" max="4"/>
-    <col width="9.895287958115183" customWidth="1" min="5" max="5"/>
-    <col width="6.596858638743456" customWidth="1" min="6" max="6"/>
-    <col width="8.575916230366493" customWidth="1" min="7" max="7"/>
-    <col width="8.575916230366493" customWidth="1" min="8" max="8"/>
+    <col width="22.7710843373494" customWidth="1" min="1" max="1"/>
+    <col width="38.71084337349398" customWidth="1" min="2" max="2"/>
+    <col width="9.867469879518072" customWidth="1" min="3" max="3"/>
+    <col width="15.93975903614458" customWidth="1" min="4" max="4"/>
+    <col width="11.3855421686747" customWidth="1" min="5" max="5"/>
+    <col width="7.590361445783133" customWidth="1" min="6" max="6"/>
+    <col width="9.867469879518072" customWidth="1" min="7" max="7"/>
+    <col width="9.867469879518072" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2461,42 +2461,61 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Rows are replaced from the latest namespace snapshot.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Pod</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CPU Current</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Memory Current (GB)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Observed Time</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Restarts</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Namespace</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Pod</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>CPU Current</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Memory Current (GB)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Observed Time</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Restarts</t>
-        </is>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>dgh-ns</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>elasticsearch-cluster-es-default-0</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1.582031</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>05:07:23</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2507,18 +2526,18 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>elasticsearch-cluster-es-default-0</t>
+          <t>logstash-ls-0</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1.582031</v>
+        <v>1.499023</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -2533,18 +2552,18 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>logstash-ls-0</t>
+          <t>ims-financial-service-7f65f7f79c-62l58</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.498047</v>
+        <v>0.588867</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -2554,23 +2573,23 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>dgh-ns</t>
+          <t>keycloak</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ims-financial-service-7f65f7f79c-62l58</t>
+          <t>keycloak-58df4c66dd-s5bqk</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.588867</v>
+        <v>0.487305</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -2580,23 +2599,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>keycloak</t>
+          <t>dgh-ns</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>keycloak-58df4c66dd-s5bqk</t>
+          <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.487305</v>
+        <v>0.420898</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
@@ -2611,18 +2630,18 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ims-workflow-query-audit-service-57b5667fd8-w2lvn</t>
+          <t>ims-udm-service-6b56656f56-9wk8d</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.420898</v>
+        <v>0.393555</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -2637,18 +2656,18 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ims-udm-service-6b56656f56-9wk8d</t>
+          <t>ims-master-data-service-7568c4c56b-6srt6</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.392578</v>
+        <v>0.388672</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -2670,11 +2689,11 @@
         <v>0.001</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.388672</v>
+        <v>0.387695</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -2689,18 +2708,18 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ims-master-data-service-7568c4c56b-6srt6</t>
+          <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.386719</v>
+        <v>0.370117</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -2715,53 +2734,26 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ims-technical-regulation-service-79f6649fcc-ghglv</t>
+          <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.370117</v>
+        <v>0.361328</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>22:49:08</t>
+          <t>05:07:23</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>dgh-ns</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ims-work-flow-service-6848d88b4d-zmr4b</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.360352</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>22:49:08</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
